--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/antofagasta.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M481"/>
+  <dimension ref="A1:M484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>829.84</v>
+        <v>825.5700000000001</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>26105.99</v>
+        <v>25971.85</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>848.61</v>
+        <v>844.25</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>4974.6</v>
+        <v>4924.96</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>31104.17</v>
+        <v>30793.75</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7759.63</v>
+        <v>7682.19</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3016.91</v>
+        <v>2985.32</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3372.76</v>
+        <v>3337.44</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5448.55</v>
+        <v>5391.5</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>908.3</v>
+        <v>898.79</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>21620.24</v>
+        <v>21502.06</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1656.45</v>
+        <v>1647.4</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>746.92</v>
+        <v>742.83</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>887.99</v>
+        <v>883.14</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>773.3099999999999</v>
+        <v>769.08</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1471.04</v>
+        <v>1469.17</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1014.75</v>
+        <v>1013.46</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>8667.9</v>
+        <v>8698.83</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3776.04</v>
+        <v>3817.11</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>775.78</v>
+        <v>784.22</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7290.03</v>
+        <v>7314</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>857.97</v>
+        <v>860.8</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2148.8</v>
+        <v>2155.86</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>779.09</v>
+        <v>781.65</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>6695.97</v>
+        <v>6717.99</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1156.43</v>
+        <v>1160.23</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>6676.07</v>
+        <v>6698.03</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1848.02</v>
+        <v>1854.1</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>6225.08</v>
+        <v>6245.56</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>4628.38</v>
+        <v>4643.61</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>15795.74</v>
+        <v>15847.7</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7745.13</v>
+        <v>7781.2</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>19067.44</v>
+        <v>19204.91</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>6311.84</v>
+        <v>6357.34</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>10697.31</v>
+        <v>10774.43</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2076.11</v>
+        <v>2067.56</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1619.89</v>
+        <v>1631.33</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>15519.26</v>
+        <v>15628.79</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>4091.52</v>
+        <v>4050.81</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>788.0700000000001</v>
+        <v>780.23</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>8702.6</v>
+        <v>8616.01</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1125.2</v>
+        <v>1122.76</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1530.41</v>
+        <v>1527.1</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>958.77</v>
+        <v>954.75</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1395.29</v>
+        <v>1389.44</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1983.8</v>
+        <v>1975.49</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2249.61</v>
+        <v>2240.18</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1325.24</v>
+        <v>1319.68</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>786.3</v>
+        <v>777.2</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>824.8</v>
+        <v>815.25</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>11636.16</v>
+        <v>11537.59</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3855.87</v>
+        <v>3852.77</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>918.6799999999999</v>
+        <v>917.9400000000001</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>3881.06</v>
+        <v>3877.94</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>787.17</v>
+        <v>786.54</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>10396</v>
+        <v>10387.64</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>9607.15</v>
+        <v>9599.43</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5290.45</v>
+        <v>5286.2</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1480.55</v>
+        <v>1479.36</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>4249.08</v>
+        <v>4245.66</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1344.36</v>
+        <v>1349.52</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1457.36</v>
+        <v>1462.95</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1324.87</v>
+        <v>1329.96</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>18254.72</v>
+        <v>18324.78</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3631.71</v>
+        <v>3648.17</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2464.45</v>
+        <v>2470.98</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1182.95</v>
+        <v>1186.09</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2838.15</v>
+        <v>2845.68</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>18680.41</v>
+        <v>18654.2</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1219.99</v>
+        <v>1221.55</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>7947.55</v>
+        <v>7957.74</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>5961.66</v>
+        <v>5969.3</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>8238.889999999999</v>
+        <v>8249.459999999999</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>39746.2</v>
+        <v>39797.16</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>16764.45</v>
+        <v>16785.95</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>11317.8</v>
+        <v>11395.7</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3948.12</v>
+        <v>3981.86</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1094.07</v>
+        <v>1103.42</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>791.03</v>
+        <v>801.1900000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>7531.71</v>
+        <v>7628.49</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>47629.2</v>
+        <v>47889.67</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>828.83</v>
+        <v>833.36</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>4572.11</v>
+        <v>4597.12</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2219.81</v>
+        <v>2231.95</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>7417.04</v>
+        <v>7227.64</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>28844.62</v>
+        <v>28108.05</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>7111.51</v>
+        <v>6929.91</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1153.75</v>
+        <v>1131.25</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>5718.95</v>
+        <v>5607.41</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1716.95</v>
+        <v>1676.79</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>22212.4</v>
+        <v>21692.78</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>26678.57</v>
+        <v>26054.47</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>5767.15</v>
+        <v>5632.23</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>7932.13</v>
+        <v>7746.57</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2774.73</v>
+        <v>2734.75</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>6547.88</v>
+        <v>6463.25</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>8198.4</v>
+        <v>8198.450000000001</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>5273.09</v>
+        <v>5280.41</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>5192.54</v>
+        <v>5199.75</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>938.29</v>
+        <v>939.6</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>6180.87</v>
+        <v>6189.45</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1894.11</v>
+        <v>1892.82</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>14149.7</v>
+        <v>14140.04</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>15201.47</v>
+        <v>15191.08</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1093.12</v>
+        <v>1089.37</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>8157.99</v>
+        <v>8129.99</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>5355.21</v>
+        <v>5326.92</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1025.61</v>
+        <v>1020.19</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1502.2</v>
+        <v>1494.26</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>932.92</v>
+        <v>927.99</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>19315.53</v>
+        <v>19213.5</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>19196.04</v>
+        <v>19094.64</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>12499.52</v>
+        <v>12433.5</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>24129.94</v>
+        <v>24002.47</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>18542.58</v>
+        <v>18444.63</v>
       </c>
     </row>
     <row r="117">
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>3226.69</v>
+        <v>3206.47</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1346284-7-CM26</t>
+          <t>3391-63-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1283.36</v>
+        <v>4863.39</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>3391-63-CM26</t>
+          <t>1346284-7-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7676,12 +7676,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>4894.06</v>
+        <v>1275.32</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3391-62-CM26</t>
+          <t>3391-61-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>5043.54</v>
+        <v>1321.66</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3391-61-CM26</t>
+          <t>3391-62-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1329.99</v>
+        <v>5011.94</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1275.84</v>
+        <v>1267.84</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>1972.06</v>
+        <v>1984.99</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3129.93</v>
+        <v>3150.44</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2305.66</v>
+        <v>2336.71</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>5767.15</v>
+        <v>5844.81</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2914.07</v>
+        <v>2958.44</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>7676.61</v>
+        <v>7863.28</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>804.09</v>
+        <v>823.64</v>
       </c>
     </row>
     <row r="130">
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2333.65</v>
+        <v>2390.4</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>3391-71-CM26</t>
+          <t>3391-75-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>FARMANOSTICA SPA</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>76.739.523-K</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1384.12</v>
+        <v>1020.14</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3391-75-CM26</t>
+          <t>3391-71-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>FARMANOSTICA SPA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>76.739.523-K</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>995.92</v>
+        <v>1417.77</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3391-69-CM26</t>
+          <t>3391-70-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>BLUNDING S.A.</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>79.744.580-0</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1718.06</v>
+        <v>866.66</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3391-68-CM26</t>
+          <t>3391-69-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>DIFEM LABORATORIOS S A</t>
+          <t>BLUNDING S.A.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>79.581.120-6</t>
+          <t>79.744.580-0</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>3072.78</v>
+        <v>1759.84</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>3391-67-CM26</t>
+          <t>3391-68-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>DIFEM LABORATORIOS S A</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>79.581.120-6</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>846.2</v>
+        <v>3147.5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>3391-70-CM26</t>
+          <t>3391-67-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>846.09</v>
+        <v>866.78</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>15272.76</v>
+        <v>15658.86</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>4882.99</v>
+        <v>5006.43</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>6747.11</v>
+        <v>6917.68</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>5733.76</v>
+        <v>5878.71</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>4899.25</v>
+        <v>5047.81</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>1362.76</v>
+        <v>1404.09</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>871.9</v>
+        <v>898.34</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>23962.8</v>
+        <v>24675.04</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>858.9299999999999</v>
+        <v>855.87</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1159.73</v>
+        <v>1155.6</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1048.34</v>
+        <v>1044.6</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1153.79</v>
+        <v>1149.68</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2021.02</v>
+        <v>2031.46</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>829.92</v>
+        <v>835.39</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>14440.97</v>
+        <v>14569.59</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>14170.79</v>
+        <v>14297</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2535.66</v>
+        <v>2533.05</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>2154.53</v>
+        <v>2152.3</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>4705.42</v>
+        <v>4671.71</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>46095.09</v>
+        <v>45764.86</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2072.39</v>
+        <v>2057.54</v>
       </c>
     </row>
     <row r="158">
@@ -10085,13 +10085,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>25352.9</v>
+        <v>25171.27</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2215-119-CM26</t>
+          <t>2215-117-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>59.077.290-9</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>8380.33</v>
+        <v>4570.93</v>
       </c>
     </row>
     <row r="160">
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3169.11</v>
+        <v>3164.45</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2215-117-CM26</t>
+          <t>2215-110-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10253,12 +10253,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>59.077.290-9</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>4577.67</v>
+        <v>4078.83</v>
       </c>
     </row>
     <row r="162">
@@ -10329,13 +10329,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>7887.5</v>
+        <v>7875.9</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2215-115-CM26</t>
+          <t>2215-119-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>37562.82</v>
+        <v>8368</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2215-108-CM26</t>
+          <t>2215-115-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>MEDIPLEX S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>86.383.300-0</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -10451,13 +10451,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>20421.14</v>
+        <v>37507.56</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2215-113-CM26</t>
+          <t>2215-108-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>MEDIPLEX S A</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>86.383.300-0</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10512,13 +10512,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>11459.35</v>
+        <v>20391.1</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2215-112-CM26</t>
+          <t>2215-113-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10558,12 +10558,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>1651.05</v>
+        <v>11442.49</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2215-111-CM26</t>
+          <t>2215-112-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>3468.45</v>
+        <v>1648.62</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2215-110-CM26</t>
+          <t>2215-111-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>4084.84</v>
+        <v>3463.35</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2215-114-CM26</t>
+          <t>2258-1524-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10741,12 +10741,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>59.077.290-9</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>2288.83</v>
+        <v>5049.25</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2258-1524-CM26</t>
+          <t>2215-114-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>59.077.290-9</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>5056.69</v>
+        <v>2285.47</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2258-1529-CM26</t>
+          <t>2258-1527-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>6489.28</v>
+        <v>13673.45</v>
       </c>
     </row>
     <row r="172">
@@ -10939,13 +10939,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>2226.84</v>
+        <v>2214.72</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2258-1555-CM26</t>
+          <t>2258-1529-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>19050.6</v>
+        <v>6453.95</v>
       </c>
     </row>
     <row r="174">
@@ -11061,13 +11061,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2146.87</v>
+        <v>2135.18</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2258-1527-CM26</t>
+          <t>2258-1555-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11107,12 +11107,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>13748.32</v>
+        <v>18946.86</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>2816.18</v>
+        <v>2800.84</v>
       </c>
     </row>
     <row r="177">
@@ -11244,13 +11244,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>2774.76</v>
+        <v>2759.65</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1261592-154-CM26</t>
+          <t>2258-1518-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11275,12 +11275,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11290,12 +11290,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>DIFEM LABORATORIOS S A</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>79.581.120-6</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11305,13 +11305,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>2297.34</v>
+        <v>5995.94</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2258-1518-CM26</t>
+          <t>2258-1515-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>DIFEM LABORATORIOS S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>79.581.120-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>6028.77</v>
+        <v>3447.78</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2258-1515-CM26</t>
+          <t>1261592-154-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11397,12 +11397,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11412,12 +11412,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>3466.66</v>
+        <v>2284.83</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>1116.2</v>
+        <v>1109.62</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>1651.52</v>
+        <v>1645.15</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>890.41</v>
+        <v>886.97</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1108.17</v>
+        <v>1103.89</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>4577.67</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>77444.84</v>
+        <v>77145.92999999999</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>7028.43</v>
+        <v>7001.3</v>
       </c>
     </row>
     <row r="188">
@@ -11915,13 +11915,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>872.13</v>
+        <v>868.76</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2258-1756-CM26</t>
+          <t>2258-1726-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11961,12 +11961,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>DELTAMED LIMITADA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>76.512.686-k</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -11976,13 +11976,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>4175.95</v>
+        <v>2371.45</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2258-1726-CM26</t>
+          <t>2258-1756-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12022,12 +12022,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>DELTAMED LIMITADA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>76.512.686-k</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>2359.24</v>
+        <v>4197.57</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>823.12</v>
+        <v>823.91</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>3040.74</v>
+        <v>3175.03</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>2481.43</v>
+        <v>2553.5</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>778.27</v>
+        <v>781.34</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1229.38</v>
+        <v>1234.22</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>1076.12</v>
+        <v>1080.36</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1435.02</v>
+        <v>1440.68</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>24258.74</v>
+        <v>24354.38</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>30946.08</v>
+        <v>31068.09</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>2320.45</v>
+        <v>2329.6</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>2246.49</v>
+        <v>2255.34</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>828.65</v>
+        <v>831.92</v>
       </c>
     </row>
     <row r="203">
@@ -12830,13 +12830,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>1178.7</v>
+        <v>1181.6</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1261592-209-CM26</t>
+          <t>1261592-205-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12876,12 +12876,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -12891,13 +12891,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>1477.87</v>
+        <v>2099.66</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1261592-208-CM26</t>
+          <t>1261592-206-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12937,12 +12937,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>MADEGOM S.A.</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>84.609.600-0</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -12952,13 +12952,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>941.65</v>
+        <v>1126.38</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1261592-205-CM26</t>
+          <t>1261592-208-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -13013,13 +13013,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>2127.04</v>
+        <v>929.53</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1261592-206-CM26</t>
+          <t>1261592-209-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13059,12 +13059,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>MADEGOM S.A.</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>84.609.600-0</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -13074,13 +13074,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1141.07</v>
+        <v>1458.84</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>3391-171-CM26</t>
+          <t>2258-2017-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13120,12 +13120,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>SOC DISTRIBUIDORA COMERCIAL E INVERSIONES LAURA CARE LTDA</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>78.634.170-1</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -13135,13 +13135,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>908.17</v>
+        <v>7407.18</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2258-2017-CM26</t>
+          <t>3391-171-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13166,12 +13166,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13181,12 +13181,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>SOC DISTRIBUIDORA COMERCIAL E INVERSIONES LAURA CARE LTDA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>78.634.170-1</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>7459.82</v>
+        <v>901.76</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>782.09</v>
+        <v>796.27</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>9203.530000000001</v>
+        <v>9347.700000000001</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1620.03</v>
+        <v>1645.41</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>823.9400000000001</v>
+        <v>823.9</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>3503.57</v>
+        <v>3493.91</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>5642.88</v>
+        <v>5627.31</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>7873.48</v>
+        <v>7851.77</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1171.83</v>
+        <v>1168.6</v>
       </c>
     </row>
     <row r="218">
@@ -13745,13 +13745,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>1321.24</v>
+        <v>1317.59</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2258-2346-CM26</t>
+          <t>2215-300-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>DIFEM LABORATORIOS S A</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>79.581.120-6</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -13806,13 +13806,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>880.7</v>
+        <v>9409.389999999999</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2215-300-CM26</t>
+          <t>2215-299-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13852,12 +13852,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>DIFEM LABORATORIOS S A</t>
+          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>79.581.120-6</t>
+          <t>59.077.290-9</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -13867,13 +13867,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>9519.290000000001</v>
+        <v>1978.45</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2215-299-CM26</t>
+          <t>2215-298-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13913,12 +13913,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>59.077.290-9</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -13928,13 +13928,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>2001.55</v>
+        <v>15030.06</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2215-297-CM26</t>
+          <t>2258-2346-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13959,12 +13959,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -13974,12 +13974,12 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>DOLPHIN MEDICAL</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>77.783.690-0</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>13218.4</v>
+        <v>870.53</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>11476.09</v>
+        <v>11343.6</v>
       </c>
     </row>
     <row r="224">
@@ -14111,13 +14111,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1048.79</v>
+        <v>1036.68</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2215-298-CM26</t>
+          <t>2215-297-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14157,12 +14157,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>DOLPHIN MEDICAL</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>77.783.690-0</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -14172,13 +14172,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>15205.6</v>
+        <v>13065.8</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2215-295-CM26</t>
+          <t>2215-309-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14218,12 +14218,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>BLUNDING S.A.</t>
+          <t>MEDIPLEX S A</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>79.744.580-0</t>
+          <t>86.383.300-0</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -14233,13 +14233,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>32425.68</v>
+        <v>6309.51</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2215-301-CM26</t>
+          <t>2215-308-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>SOLUCIONES MÉDICAS SPA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>76.781.234-5</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -14294,13 +14294,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>3002.37</v>
+        <v>5363.1</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2215-302-CM26</t>
+          <t>2215-305-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>MADEGOM S.A.</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>84.609.600-0</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -14355,13 +14355,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>884.05</v>
+        <v>3021.15</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2215-303-CM26</t>
+          <t>2215-304-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14401,12 +14401,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>GERMÁN BERNARDO BEHNKE GUTIÉRREZ</t>
+          <t>DELTAMED LIMITADA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>5.892.120-3</t>
+          <t>76.512.686-k</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -14416,13 +14416,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>4708.15</v>
+        <v>19434.59</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2215-304-CM26</t>
+          <t>2215-307-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14462,12 +14462,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>DELTAMED LIMITADA</t>
+          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>76.512.686-k</t>
+          <t>59.077.290-9</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -14477,13 +14477,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>19728.85</v>
+        <v>6746.06</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2215-305-CM26</t>
+          <t>2215-302-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14523,12 +14523,12 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>MADEGOM S.A.</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>84.609.600-0</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -14538,13 +14538,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>3066.9</v>
+        <v>870.86</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2215-307-CM26</t>
+          <t>2215-301-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14584,12 +14584,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>59.077.290-9</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -14599,13 +14599,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>6848.21</v>
+        <v>2957.59</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2215-308-CM26</t>
+          <t>2215-295-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>SOLUCIONES MÉDICAS SPA</t>
+          <t>BLUNDING S.A.</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>76.781.234-5</t>
+          <t>79.744.580-0</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
@@ -14660,13 +14660,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>5444.3</v>
+        <v>31942.04</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2215-309-CM26</t>
+          <t>2215-303-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14706,12 +14706,12 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>MEDIPLEX S A</t>
+          <t>GERMÁN BERNARDO BEHNKE GUTIÉRREZ</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>86.383.300-0</t>
+          <t>5.892.120-3</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>6405.04</v>
+        <v>4637.92</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>4080.48</v>
+        <v>4062.9</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>18610.32</v>
+        <v>18530.15</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>3789.93</v>
+        <v>3735.1</v>
       </c>
     </row>
     <row r="238">
@@ -14965,13 +14965,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2687.62</v>
+        <v>2629.8</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2258-2561-CM26</t>
+          <t>2258-2545-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15026,13 +15026,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>40582.46</v>
+        <v>5638.9</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2258-2545-CM26</t>
+          <t>2430-69-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15057,12 +15057,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15072,12 +15072,12 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>BLUNDING S.A.</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>79.744.580-0</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -15087,13 +15087,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>5762.89</v>
+        <v>867.01</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2430-69-CM26</t>
+          <t>2258-2561-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15118,12 +15118,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15133,12 +15133,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>BLUNDING S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>79.744.580-0</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -15148,13 +15148,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>886.0700000000001</v>
+        <v>39709.33</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2215-383-CM26</t>
+          <t>2258-2646-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15179,12 +15179,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>59.077.290-9</t>
+          <t>77.237.150-0</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -15209,13 +15209,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1752.56</v>
+        <v>12055.88</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2258-2646-CM26</t>
+          <t>2215-383-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15240,12 +15240,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15255,12 +15255,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
+          <t>59.077.290-9</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>12343.1</v>
+        <v>1711.77</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>4745.36</v>
+        <v>4594.05</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>34000.01</v>
+        <v>32915.86</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>811.33</v>
+        <v>785.46</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>4731.8</v>
+        <v>4580.91</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>4068.25</v>
+        <v>3938.52</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1491</v>
+        <v>1443.46</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>864.37</v>
+        <v>836.8099999999999</v>
       </c>
     </row>
     <row r="251">
@@ -15758,13 +15758,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>1024.21</v>
+        <v>1004.01</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2258-2791-CM26</t>
+          <t>2258-2786-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15819,13 +15819,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>3816.96</v>
+        <v>2555.06</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2258-2786-CM26</t>
+          <t>2258-2791-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>2624.16</v>
+        <v>3716.45</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>44732.8</v>
+        <v>43554.84</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>29488.7</v>
+        <v>28953.93</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>791.17</v>
+        <v>769.99</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>28945.32</v>
+        <v>28170.26</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1763.15</v>
+        <v>1768.28</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>4241.07</v>
+        <v>4258.7</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>14117.2</v>
+        <v>14175.87</v>
       </c>
     </row>
     <row r="261">
@@ -16368,13 +16368,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>2742.48</v>
+        <v>2765.75</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>769-237-CM26</t>
+          <t>1261592-331-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16399,12 +16399,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K262" t="inlineStr"/>
@@ -16429,13 +16429,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>3601.28</v>
+        <v>935.9299999999999</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1261592-341-CM26</t>
+          <t>769-237-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16475,12 +16475,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
@@ -16490,13 +16490,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>4595.28</v>
+        <v>3645.6</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1261592-340-CM26</t>
+          <t>1261592-341-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16536,12 +16536,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>MEDICALTEK CHILE S A</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>96.696.000-0</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>1516.98</v>
+        <v>4651.84</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>1988</v>
+        <v>2012.47</v>
       </c>
     </row>
     <row r="266">
@@ -16673,13 +16673,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>6416.34</v>
+        <v>6495.31</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1261592-331-CM26</t>
+          <t>1261592-340-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -16719,12 +16719,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>MEDICALTEK CHILE S A</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>96.696.000-0</t>
         </is>
       </c>
       <c r="K267" t="inlineStr"/>
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>924.55</v>
+        <v>1535.65</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>980.75</v>
+        <v>992.8200000000001</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>1199.36</v>
+        <v>1214.12</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>1481.72</v>
+        <v>1499.96</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>2297.47</v>
+        <v>2325.74</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>16633.22</v>
+        <v>16837.93</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>7447.73</v>
+        <v>7546.88</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1312.08</v>
+        <v>1329.55</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>15283.1</v>
+        <v>15486.56</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>3001.88</v>
+        <v>3041.06</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>8678.58</v>
+        <v>8791.83</v>
       </c>
     </row>
     <row r="278">
@@ -17405,13 +17405,13 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>986.46</v>
+        <v>1010.74</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2215-444-CM26</t>
+          <t>2258-3323-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>MADEGOM S.A.</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>84.609.600-0</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K279" t="inlineStr"/>
@@ -17466,13 +17466,13 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>1974.75</v>
+        <v>925.6900000000001</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2258-3323-CM26</t>
+          <t>2215-459-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17497,12 +17497,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17512,12 +17512,12 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K280" t="inlineStr"/>
@@ -17527,13 +17527,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>915.28</v>
+        <v>5207.15</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2215-459-CM26</t>
+          <t>2215-447-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -17573,12 +17573,12 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K281" t="inlineStr"/>
@@ -17588,13 +17588,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>5148.6</v>
+        <v>817.8099999999999</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2215-447-CM26</t>
+          <t>2215-446-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -17634,12 +17634,12 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K282" t="inlineStr"/>
@@ -17649,13 +17649,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>808.61</v>
+        <v>5713.35</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2215-446-CM26</t>
+          <t>2215-444-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -17695,12 +17695,12 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>MADEGOM S.A.</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>84.609.600-0</t>
         </is>
       </c>
       <c r="K283" t="inlineStr"/>
@@ -17710,13 +17710,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>5649.11</v>
+        <v>1997.21</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2215-442-CM26</t>
+          <t>2215-443-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -17756,12 +17756,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K284" t="inlineStr"/>
@@ -17771,13 +17771,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>2028.29</v>
+        <v>2528.41</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2215-443-CM26</t>
+          <t>2215-442-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -17817,12 +17817,12 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K285" t="inlineStr"/>
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>2499.98</v>
+        <v>2051.36</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>1308.48</v>
+        <v>1323.36</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>5407.37</v>
+        <v>5468.86</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>5609.61</v>
+        <v>5660.15</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2721.71</v>
+        <v>2746.23</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>3115.24</v>
+        <v>3135.16</v>
       </c>
     </row>
     <row r="291">
@@ -18198,13 +18198,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>928.97</v>
+        <v>934.91</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2258-3463-CM26</t>
+          <t>2258-3459-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18244,12 +18244,12 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>59.077.290-9</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K292" t="inlineStr"/>
@@ -18259,13 +18259,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>2873.96</v>
+        <v>2346.36</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2258-3476-CM26</t>
+          <t>2258-3478-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18305,12 +18305,12 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>77.237.150-0</t>
         </is>
       </c>
       <c r="K293" t="inlineStr"/>
@@ -18320,13 +18320,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1579.27</v>
+        <v>27693.71</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2258-3462-CM26</t>
+          <t>2258-3476-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18366,12 +18366,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA HOSPITALMARKET SPA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>77.910.467-2</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K294" t="inlineStr"/>
@@ -18381,13 +18381,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>2035.56</v>
+        <v>1585.81</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2258-3478-CM26</t>
+          <t>2258-3463-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18427,12 +18427,12 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
+          <t>59.077.290-9</t>
         </is>
       </c>
       <c r="K295" t="inlineStr"/>
@@ -18442,13 +18442,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>27579.4</v>
+        <v>2885.87</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1261592-385-CM26</t>
+          <t>2258-3462-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -18473,12 +18473,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18488,12 +18488,12 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>FLEXING CHILE SPA</t>
+          <t>COMERCIALIZADORA HOSPITALMARKET SPA</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>76.592.530-4</t>
+          <t>77.910.467-2</t>
         </is>
       </c>
       <c r="K296" t="inlineStr"/>
@@ -18503,13 +18503,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>2269.5</v>
+        <v>2043.99</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2258-3459-CM26</t>
+          <t>2258-3457-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -18549,12 +18549,12 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K297" t="inlineStr"/>
@@ -18564,13 +18564,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>2336.67</v>
+        <v>12535.66</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>3391-277-CM26</t>
+          <t>1261592-385-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -18595,12 +18595,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18610,12 +18610,12 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>FLEXING CHILE SPA</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>76.592.530-4</t>
         </is>
       </c>
       <c r="K298" t="inlineStr"/>
@@ -18625,13 +18625,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>972.66</v>
+        <v>2278.91</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2258-3456-CM26</t>
+          <t>3391-277-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -18656,12 +18656,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -18671,12 +18671,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K299" t="inlineStr"/>
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>25641.09</v>
+        <v>976.6900000000001</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>1587.54</v>
+        <v>1594.12</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>794.25</v>
+        <v>797.54</v>
       </c>
     </row>
     <row r="302">
@@ -18869,13 +18869,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>857.45</v>
+        <v>861</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>3391-270-CM26</t>
+          <t>2258-3456-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -18900,12 +18900,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -18915,12 +18915,12 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K303" t="inlineStr"/>
@@ -18930,13 +18930,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>1131</v>
+        <v>25747.37</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2258-3457-CM26</t>
+          <t>3391-270-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -18976,12 +18976,12 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>77.237.150-0</t>
         </is>
       </c>
       <c r="K304" t="inlineStr"/>
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>12483.91</v>
+        <v>1135.69</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>2577.48</v>
+        <v>2566.41</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1653.09</v>
+        <v>1645.99</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>28030.84</v>
+        <v>27910.42</v>
       </c>
     </row>
     <row r="308">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>836.17</v>
+        <v>845.52</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>1789.7</v>
+        <v>1796.48</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>2671.29</v>
+        <v>2664.54</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>2909.52</v>
+        <v>2902.17</v>
       </c>
     </row>
     <row r="312">
@@ -19479,13 +19479,13 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>800.49</v>
+        <v>798.47</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2258-4052-CM26</t>
+          <t>2258-4034-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -19525,12 +19525,12 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>DIFEM LABORATORIOS S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>79.581.120-6</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K313" t="inlineStr"/>
@@ -19540,13 +19540,13 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>4945.23</v>
+        <v>9218.190000000001</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2258-4034-CM26</t>
+          <t>2258-4030-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -19586,12 +19586,12 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>77.237.150-0</t>
         </is>
       </c>
       <c r="K314" t="inlineStr"/>
@@ -19601,13 +19601,13 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>9131.43</v>
+        <v>19524.2</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2258-4030-CM26</t>
+          <t>2258-4026-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -19647,12 +19647,12 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K315" t="inlineStr"/>
@@ -19662,13 +19662,13 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>19340.46</v>
+        <v>5125.68</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2258-4026-CM26</t>
+          <t>2258-4017-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -19708,12 +19708,12 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K316" t="inlineStr"/>
@@ -19723,13 +19723,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>5077.44</v>
+        <v>40768.53</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2258-4017-CM26</t>
+          <t>2258-4010-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -19769,12 +19769,12 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K317" t="inlineStr"/>
@@ -19784,13 +19784,13 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>40384.85</v>
+        <v>45930.8</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2258-4010-CM26</t>
+          <t>2258-4052-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -19830,12 +19830,12 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>DIFEM LABORATORIOS S A</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>79.581.120-6</t>
         </is>
       </c>
       <c r="K318" t="inlineStr"/>
@@ -19845,13 +19845,13 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>45498.53</v>
+        <v>4992.21</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2258-4006-CM26</t>
+          <t>2258-4004-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -19891,12 +19891,12 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K319" t="inlineStr"/>
@@ -19906,13 +19906,13 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>3970.48</v>
+        <v>2969.49</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2258-4004-CM26</t>
+          <t>2215-580-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -19937,12 +19937,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -19952,12 +19952,12 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>ISI-MED SPA</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>77.430.568-8</t>
         </is>
       </c>
       <c r="K320" t="inlineStr"/>
@@ -19967,13 +19967,13 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>2941.55</v>
+        <v>1112.93</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2215-580-CM26</t>
+          <t>2215-579-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -20013,12 +20013,12 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>ISI-MED SPA</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>77.430.568-8</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K321" t="inlineStr"/>
@@ -20028,13 +20028,13 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>1102.45</v>
+        <v>9259.01</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2215-579-CM26</t>
+          <t>2215-577-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -20089,13 +20089,13 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>9171.870000000001</v>
+        <v>8091.34</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2215-577-CM26</t>
+          <t>2215-576-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -20135,12 +20135,12 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>59.077.290-9</t>
         </is>
       </c>
       <c r="K323" t="inlineStr"/>
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>8015.19</v>
+        <v>2179.75</v>
       </c>
     </row>
     <row r="324">
@@ -20211,13 +20211,13 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>5186.78</v>
+        <v>5236.06</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2215-576-CM26</t>
+          <t>2258-4006-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -20242,12 +20242,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -20257,12 +20257,12 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>59.077.290-9</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K325" t="inlineStr"/>
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>2159.24</v>
+        <v>4008.2</v>
       </c>
     </row>
     <row r="326">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>23222.51</v>
+        <v>23443.14</v>
       </c>
     </row>
     <row r="327">
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>6654.76</v>
+        <v>6717.98</v>
       </c>
     </row>
     <row r="328">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>13304.08</v>
+        <v>13430.48</v>
       </c>
     </row>
     <row r="329">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>18009.52</v>
+        <v>18180.63</v>
       </c>
     </row>
     <row r="330">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>1039.35</v>
+        <v>1049.22</v>
       </c>
     </row>
     <row r="331">
@@ -20638,7 +20638,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>3459.09</v>
+        <v>3491.95</v>
       </c>
     </row>
     <row r="332">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>1357.78</v>
+        <v>1370.68</v>
       </c>
     </row>
     <row r="333">
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>6918.31</v>
+        <v>6984.03</v>
       </c>
     </row>
     <row r="334">
@@ -20821,7 +20821,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>7390.24</v>
+        <v>7460.46</v>
       </c>
     </row>
     <row r="335">
@@ -20882,7 +20882,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>50253.37</v>
+        <v>50730.81</v>
       </c>
     </row>
     <row r="336">
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>1331.53</v>
+        <v>1344.19</v>
       </c>
     </row>
     <row r="337">
@@ -21004,7 +21004,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>1161.82</v>
+        <v>1172.86</v>
       </c>
     </row>
     <row r="338">
@@ -21065,13 +21065,13 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>863.65</v>
+        <v>870.08</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2258-4100-CM26</t>
+          <t>2258-4074-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -21111,12 +21111,12 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K339" t="inlineStr"/>
@@ -21126,13 +21126,13 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>826.25</v>
+        <v>29382.72</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2258-4074-CM26</t>
+          <t>1113265-46-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -21157,12 +21157,12 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>62.000.770-6</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21172,12 +21172,12 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>MADEGOM S.A.</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>84.609.600-0</t>
         </is>
       </c>
       <c r="K340" t="inlineStr"/>
@@ -21187,13 +21187,13 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>29165.44</v>
+        <v>795.3</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1113265-46-CM26</t>
+          <t>2258-4100-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -21218,12 +21218,12 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>62.000.770-6</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -21233,12 +21233,12 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>MADEGOM S.A.</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>84.609.600-0</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K341" t="inlineStr"/>
@@ -21248,13 +21248,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>789.42</v>
+        <v>832.41</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1113265-43-CM26</t>
+          <t>1113265-44-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -21294,12 +21294,12 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>Dipromed S.A.</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>86.397.000-8</t>
         </is>
       </c>
       <c r="K342" t="inlineStr"/>
@@ -21309,13 +21309,13 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>1407.12</v>
+        <v>980.9</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>1113265-44-CM26</t>
+          <t>1113265-43-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -21355,12 +21355,12 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>Dipromed S.A.</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>86.397.000-8</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K343" t="inlineStr"/>
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>973.65</v>
+        <v>1417.61</v>
       </c>
     </row>
     <row r="344">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>1547.18</v>
+        <v>1558.7</v>
       </c>
     </row>
     <row r="345">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>859.77</v>
+        <v>866.1799999999999</v>
       </c>
     </row>
     <row r="346">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>6114.88</v>
+        <v>6088.07</v>
       </c>
     </row>
     <row r="347">
@@ -21614,13 +21614,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>3466.71</v>
+        <v>3451.51</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2258-4077-CM26</t>
+          <t>2258-4189-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -21660,12 +21660,12 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K348" t="inlineStr"/>
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>29601.15</v>
+        <v>14791.24</v>
       </c>
     </row>
     <row r="349">
@@ -21736,7 +21736,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>13691.85</v>
+        <v>13542.9</v>
       </c>
     </row>
     <row r="350">
@@ -21797,7 +21797,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>12999.3</v>
+        <v>12857.89</v>
       </c>
     </row>
     <row r="351">
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>2589.99</v>
+        <v>2561.82</v>
       </c>
     </row>
     <row r="352">
@@ -21919,13 +21919,13 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>898.0700000000001</v>
+        <v>888.3</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2215-549-CM26</t>
+          <t>2258-4077-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -21950,12 +21950,12 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -21965,12 +21965,12 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K353" t="inlineStr"/>
@@ -21980,13 +21980,13 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>1069.11</v>
+        <v>29279.15</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2258-4189-CM26</t>
+          <t>2215-547-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -22011,12 +22011,12 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -22026,12 +22026,12 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K354" t="inlineStr"/>
@@ -22041,13 +22041,13 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>14953.91</v>
+        <v>3647.98</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2215-547-CM26</t>
+          <t>2215-548-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -22087,12 +22087,12 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>PRONOMED SPA</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>76.286.670-6</t>
         </is>
       </c>
       <c r="K355" t="inlineStr"/>
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>3688.1</v>
+        <v>21841.87</v>
       </c>
     </row>
     <row r="356">
@@ -22163,7 +22163,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>3261.58</v>
+        <v>3226.1</v>
       </c>
     </row>
     <row r="357">
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>1156.53</v>
+        <v>1143.95</v>
       </c>
     </row>
     <row r="358">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>16637.02</v>
+        <v>16456.04</v>
       </c>
     </row>
     <row r="359">
@@ -22346,13 +22346,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>1809.54</v>
+        <v>1789.86</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2215-548-CM26</t>
+          <t>2215-549-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -22392,12 +22392,12 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>PRONOMED SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>76.286.670-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K360" t="inlineStr"/>
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>22082.08</v>
+        <v>1057.48</v>
       </c>
     </row>
     <row r="361">
@@ -22468,7 +22468,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>976.03</v>
+        <v>973.8200000000001</v>
       </c>
     </row>
     <row r="362">
@@ -22529,13 +22529,13 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>897.63</v>
+        <v>895.6</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2215-578-CM26</t>
+          <t>769-311-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -22560,12 +22560,12 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -22575,12 +22575,12 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K363" t="inlineStr"/>
@@ -22590,13 +22590,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>12053.28</v>
+        <v>32621.29</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1057997-49-CM26</t>
+          <t>2215-578-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -22621,12 +22621,12 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -22636,12 +22636,12 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K364" t="inlineStr"/>
@@ -22651,13 +22651,13 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>4209.58</v>
+        <v>12023.51</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>769-311-CM26</t>
+          <t>1057997-49-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -22682,12 +22682,12 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>32702.04</v>
+        <v>4199.18</v>
       </c>
     </row>
     <row r="366">
@@ -22773,7 +22773,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>923.05</v>
+        <v>927.58</v>
       </c>
     </row>
     <row r="367">
@@ -22834,13 +22834,13 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>10241.04</v>
+        <v>10291.35</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2258-4568-CM26</t>
+          <t>1077908-96-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -22865,12 +22865,12 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -22880,12 +22880,12 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>PRONOMED SPA</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>76.286.670-6</t>
         </is>
       </c>
       <c r="K368" t="inlineStr"/>
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>7281.42</v>
+        <v>2448.18</v>
       </c>
     </row>
     <row r="369">
@@ -22956,13 +22956,13 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>10427.29</v>
+        <v>10461.88</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>1077908-96-CM26</t>
+          <t>2258-4568-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -22987,12 +22987,12 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -23002,12 +23002,12 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>PRONOMED SPA</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>76.286.670-6</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K370" t="inlineStr"/>
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>2440.09</v>
+        <v>7305.57</v>
       </c>
     </row>
     <row r="371">
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>5992.3</v>
+        <v>6011.38</v>
       </c>
     </row>
     <row r="372">
@@ -23139,7 +23139,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>1129.92</v>
+        <v>1133.52</v>
       </c>
     </row>
     <row r="373">
@@ -23200,7 +23200,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>5859.83</v>
+        <v>5878.48</v>
       </c>
     </row>
     <row r="374">
@@ -23261,7 +23261,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>6265.27</v>
+        <v>6298.58</v>
       </c>
     </row>
     <row r="375">
@@ -23322,7 +23322,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>20872.55</v>
+        <v>20983.54</v>
       </c>
     </row>
     <row r="376">
@@ -23383,7 +23383,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>4573.56</v>
+        <v>4639</v>
       </c>
     </row>
     <row r="377">
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>17903.66</v>
+        <v>18206.45</v>
       </c>
     </row>
     <row r="378">
@@ -23505,13 +23505,13 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>2746.38</v>
+        <v>2774.31</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>1261592-567-CM26</t>
+          <t>1261592-571-CM26</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -23551,12 +23551,12 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA ALMA SALUD  SPA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>77.568.114-4</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K379" t="inlineStr"/>
@@ -23566,13 +23566,13 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>3197.01</v>
+        <v>957.33</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>1261592-568-CM26</t>
+          <t>1261592-570-CM26</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -23612,12 +23612,12 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K380" t="inlineStr"/>
@@ -23627,13 +23627,13 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>5757.39</v>
+        <v>5910.5</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>1261592-570-CM26</t>
+          <t>1261592-568-CM26</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -23673,12 +23673,12 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K381" t="inlineStr"/>
@@ -23688,13 +23688,13 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>5855.58</v>
+        <v>5811.39</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1261592-571-CM26</t>
+          <t>1261592-567-CM26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>DISTRIBUIDORA ALMA SALUD  SPA</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>77.568.114-4</t>
         </is>
       </c>
       <c r="K382" t="inlineStr"/>
@@ -23749,13 +23749,13 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>948.4299999999999</v>
+        <v>3227</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>3391-377-CM26</t>
+          <t>1261592-575-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -23780,12 +23780,12 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -23795,12 +23795,12 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K383" t="inlineStr"/>
@@ -23810,13 +23810,13 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>1225.43</v>
+        <v>1431.64</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>1261592-577-CM26</t>
+          <t>1261592-576-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -23856,12 +23856,12 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K384" t="inlineStr"/>
@@ -23871,13 +23871,13 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>1377.86</v>
+        <v>1907.05</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>1261592-575-CM26</t>
+          <t>1261592-577-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -23917,12 +23917,12 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K385" t="inlineStr"/>
@@ -23932,13 +23932,13 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>1456.24</v>
+        <v>1354.58</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>1261592-576-CM26</t>
+          <t>3391-377-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -23963,12 +23963,12 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -23978,12 +23978,12 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K386" t="inlineStr"/>
@@ -23993,7 +23993,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>1939.82</v>
+        <v>1204.72</v>
       </c>
     </row>
     <row r="387">
@@ -24054,7 +24054,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>7159.74</v>
+        <v>7061.36</v>
       </c>
     </row>
     <row r="388">
@@ -24115,7 +24115,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>4647.15</v>
+        <v>4583.3</v>
       </c>
     </row>
     <row r="389">
@@ -24176,7 +24176,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>19600.96</v>
+        <v>19479.44</v>
       </c>
     </row>
     <row r="390">
@@ -24237,7 +24237,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>991.85</v>
+        <v>996.36</v>
       </c>
     </row>
     <row r="391">
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>1574.67</v>
+        <v>1604.61</v>
       </c>
     </row>
     <row r="392">
@@ -24359,7 +24359,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>805.36</v>
+        <v>820.67</v>
       </c>
     </row>
     <row r="393">
@@ -24420,13 +24420,13 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>1111.82</v>
+        <v>1132.96</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2215-697-CM26</t>
+          <t>2215-712-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -24466,12 +24466,12 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K394" t="inlineStr"/>
@@ -24481,13 +24481,13 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>1886.42</v>
+        <v>2363.74</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2215-691-CM26</t>
+          <t>2215-697-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -24542,13 +24542,13 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>4821.2</v>
+        <v>1928.96</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2215-696-CM26</t>
+          <t>2215-691-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -24588,12 +24588,12 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K396" t="inlineStr"/>
@@ -24603,13 +24603,13 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>13492.06</v>
+        <v>4929.93</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2215-712-CM26</t>
+          <t>2215-696-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -24649,12 +24649,12 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K397" t="inlineStr"/>
@@ -24664,13 +24664,13 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>2311.61</v>
+        <v>13796.34</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2258-5250-CM26</t>
+          <t>3391-399-CM26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -24695,12 +24695,12 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -24710,12 +24710,12 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>DIFEM LABORATORIOS S A</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>79.581.120-6</t>
         </is>
       </c>
       <c r="K398" t="inlineStr"/>
@@ -24725,13 +24725,13 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>14381.94</v>
+        <v>3423.27</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2258-5244-CM26</t>
+          <t>2215-718-CM26</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -24756,12 +24756,12 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -24771,12 +24771,12 @@
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>CONVATEC CHILE S.A.</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.020.266-5</t>
         </is>
       </c>
       <c r="K399" t="inlineStr"/>
@@ -24786,13 +24786,13 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>11012.24</v>
+        <v>15092.43</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>3391-399-CM26</t>
+          <t>3391-411-CM26</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -24832,12 +24832,12 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>DIFEM LABORATORIOS S A</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>79.581.120-6</t>
+          <t>77.237.150-0</t>
         </is>
       </c>
       <c r="K400" t="inlineStr"/>
@@ -24847,13 +24847,13 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>3412.72</v>
+        <v>8380.809999999999</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2215-718-CM26</t>
+          <t>2258-5244-CM26</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -24878,12 +24878,12 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -24893,12 +24893,12 @@
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>CONVATEC CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>76.020.266-5</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K401" t="inlineStr"/>
@@ -24908,13 +24908,13 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>15045.91</v>
+        <v>11046.28</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>3391-411-CM26</t>
+          <t>2258-5250-CM26</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -24939,12 +24939,12 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -24954,12 +24954,12 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K402" t="inlineStr"/>
@@ -24969,7 +24969,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>8354.98</v>
+        <v>14426.4</v>
       </c>
     </row>
     <row r="403">
@@ -25030,7 +25030,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>1919.12</v>
+        <v>1893.55</v>
       </c>
     </row>
     <row r="404">
@@ -25091,13 +25091,13 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>2747.56</v>
+        <v>2710.96</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>3391-428-CM26</t>
+          <t>3391-423-CM26</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -25137,12 +25137,12 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K405" t="inlineStr"/>
@@ -25152,13 +25152,13 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>1075.6</v>
+        <v>909.16</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>3391-431-CM26</t>
+          <t>2258-5369-CM26</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -25183,12 +25183,12 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -25198,12 +25198,12 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.237.150-0</t>
         </is>
       </c>
       <c r="K406" t="inlineStr"/>
@@ -25213,13 +25213,13 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>2209.01</v>
+        <v>1185.93</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>3391-427-CM26</t>
+          <t>1261592-666-CM26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -25244,12 +25244,12 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -25259,12 +25259,12 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K407" t="inlineStr"/>
@@ -25274,13 +25274,13 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>2460.92</v>
+        <v>3874.45</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2258-5372-CM26</t>
+          <t>1261592-665-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -25305,12 +25305,12 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -25320,12 +25320,12 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K408" t="inlineStr"/>
@@ -25335,13 +25335,13 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>18146.7</v>
+        <v>3579.75</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2258-5369-CM26</t>
+          <t>3391-431-CM26</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -25366,12 +25366,12 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -25381,12 +25381,12 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K409" t="inlineStr"/>
@@ -25396,13 +25396,13 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>1209.6</v>
+        <v>2165.77</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>1261592-665-CM26</t>
+          <t>3391-428-CM26</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -25427,12 +25427,12 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -25442,12 +25442,12 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K410" t="inlineStr"/>
@@ -25457,13 +25457,13 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>3651.22</v>
+        <v>1054.55</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>3391-426-CM26</t>
+          <t>3391-427-CM26</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -25503,12 +25503,12 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>COMERCIAL LIMAX SPA</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>76.719.400-5</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K411" t="inlineStr"/>
@@ -25518,13 +25518,13 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>1168.56</v>
+        <v>2412.75</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>1261592-666-CM26</t>
+          <t>3391-426-CM26</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -25549,12 +25549,12 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -25564,12 +25564,12 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL LIMAX SPA</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>76.719.400-5</t>
         </is>
       </c>
       <c r="K412" t="inlineStr"/>
@@ -25579,13 +25579,13 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>3951.81</v>
+        <v>1145.69</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>3391-424-CM26</t>
+          <t>3391-422-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -25625,12 +25625,12 @@
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>GREENWICH MEDICAL SPA</t>
+          <t>MADEGOM S.A.</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>77.054.028-3</t>
+          <t>84.609.600-0</t>
         </is>
       </c>
       <c r="K413" t="inlineStr"/>
@@ -25640,13 +25640,13 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>1041.41</v>
+        <v>2130.9</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>3391-423-CM26</t>
+          <t>3391-424-CM26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -25686,12 +25686,12 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>GREENWICH MEDICAL SPA</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>77.054.028-3</t>
         </is>
       </c>
       <c r="K414" t="inlineStr"/>
@@ -25701,13 +25701,13 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>927.3200000000001</v>
+        <v>1021.03</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>3391-422-CM26</t>
+          <t>2258-5372-CM26</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -25732,12 +25732,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -25747,12 +25747,12 @@
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>MADEGOM S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>84.609.600-0</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K415" t="inlineStr"/>
@@ -25762,7 +25762,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>2173.44</v>
+        <v>17791.5</v>
       </c>
     </row>
     <row r="416">
@@ -25823,7 +25823,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>1900.04</v>
+        <v>1862.85</v>
       </c>
     </row>
     <row r="417">
@@ -25884,7 +25884,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>2681.81</v>
+        <v>2629.31</v>
       </c>
     </row>
     <row r="418">
@@ -25945,7 +25945,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>933.71</v>
+        <v>915.4299999999999</v>
       </c>
     </row>
     <row r="419">
@@ -26006,7 +26006,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>4215.26</v>
+        <v>4132.75</v>
       </c>
     </row>
     <row r="420">
@@ -26067,7 +26067,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>1542.89</v>
+        <v>1512.69</v>
       </c>
     </row>
     <row r="421">
@@ -26128,13 +26128,13 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>2276.24</v>
+        <v>2242.52</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>3391-432-CM26</t>
+          <t>1261592-743-CM26</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -26159,12 +26159,12 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -26174,12 +26174,12 @@
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K422" t="inlineStr"/>
@@ -26189,7 +26189,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>2520.76</v>
+        <v>1050.48</v>
       </c>
     </row>
     <row r="423">
@@ -26250,13 +26250,13 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>3487.24</v>
+        <v>3415.57</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>1261592-743-CM26</t>
+          <t>3391-432-CM26</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -26281,12 +26281,12 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -26296,12 +26296,12 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K424" t="inlineStr"/>
@@ -26311,7 +26311,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>1072.52</v>
+        <v>2468.95</v>
       </c>
     </row>
     <row r="425">
@@ -26372,13 +26372,13 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>21627.76</v>
+        <v>21833.21</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>1261592-781-CM26</t>
+          <t>1261592-756-CM26</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -26418,12 +26418,12 @@
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>Dipromed S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>86.397.000-8</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K426" t="inlineStr"/>
@@ -26433,13 +26433,13 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>2217.17</v>
+        <v>7421.12</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>1261592-780-CM26</t>
+          <t>1261592-758-CM26</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -26494,13 +26494,13 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>1796.68</v>
+        <v>2003.5</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>1261592-779-CM26</t>
+          <t>1261592-771-CM26</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -26555,13 +26555,13 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>5611.49</v>
+        <v>7543.06</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>1261592-777-CM26</t>
+          <t>1261592-775-CM26</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -26601,12 +26601,12 @@
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K429" t="inlineStr"/>
@@ -26616,13 +26616,13 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>10204.01</v>
+        <v>1418.85</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>1261592-771-CM26</t>
+          <t>1261592-776-CM26</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -26662,12 +26662,12 @@
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K430" t="inlineStr"/>
@@ -26677,13 +26677,13 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>7468.28</v>
+        <v>17971.23</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>1261592-775-CM26</t>
+          <t>1261592-777-CM26</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -26723,12 +26723,12 @@
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K431" t="inlineStr"/>
@@ -26738,13 +26738,13 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>1404.78</v>
+        <v>10306.19</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>1261592-758-CM26</t>
+          <t>1261592-779-CM26</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -26784,12 +26784,12 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>Dipromed S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>86.397.000-8</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K432" t="inlineStr"/>
@@ -26799,13 +26799,13 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>1983.63</v>
+        <v>5667.68</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>1261592-756-CM26</t>
+          <t>1261592-780-CM26</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -26845,12 +26845,12 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Dipromed S.A.</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>86.397.000-8</t>
         </is>
       </c>
       <c r="K433" t="inlineStr"/>
@@ -26860,13 +26860,13 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>7347.54</v>
+        <v>1814.68</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>1261592-776-CM26</t>
+          <t>1261592-781-CM26</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -26906,12 +26906,12 @@
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>Dipromed S.A.</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>86.397.000-8</t>
         </is>
       </c>
       <c r="K434" t="inlineStr"/>
@@ -26921,7 +26921,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>17793.05</v>
+        <v>2239.37</v>
       </c>
     </row>
     <row r="435">
@@ -26982,7 +26982,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>8935.639999999999</v>
+        <v>8970.43</v>
       </c>
     </row>
     <row r="436">
@@ -27043,7 +27043,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>3811.7</v>
+        <v>3826.54</v>
       </c>
     </row>
     <row r="437">
@@ -27104,7 +27104,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>2843.38</v>
+        <v>2861.92</v>
       </c>
     </row>
     <row r="438">
@@ -27165,7 +27165,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>4475.67</v>
+        <v>4485.93</v>
       </c>
     </row>
     <row r="439">
@@ -27226,7 +27226,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>5563.32</v>
+        <v>5576.08</v>
       </c>
     </row>
     <row r="440">
@@ -27287,7 +27287,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>3728.83</v>
+        <v>3737.38</v>
       </c>
     </row>
     <row r="441">
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>3911.4</v>
+        <v>3920.37</v>
       </c>
     </row>
     <row r="442">
@@ -27409,13 +27409,13 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>8248.969999999999</v>
+        <v>8267.889999999999</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>2258-5799-CM26</t>
+          <t>2215-758-CM26</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -27440,12 +27440,12 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -27455,12 +27455,12 @@
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K443" t="inlineStr"/>
@@ -27470,13 +27470,13 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>30055.43</v>
+        <v>844.78</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2215-760-CM26</t>
+          <t>2215-759-CM26</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -27531,13 +27531,13 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>10005.91</v>
+        <v>6053.75</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>2258-5917-CM26</t>
+          <t>2215-760-CM26</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -27562,12 +27562,12 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -27577,12 +27577,12 @@
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K445" t="inlineStr"/>
@@ -27592,13 +27592,13 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>4059.68</v>
+        <v>10072.88</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>2215-758-CM26</t>
+          <t>2258-5799-CM26</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -27623,12 +27623,12 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -27638,12 +27638,12 @@
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K446" t="inlineStr"/>
@@ -27653,13 +27653,13 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>839.16</v>
+        <v>30256.61</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>2215-759-CM26</t>
+          <t>2258-5917-CM26</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -27684,12 +27684,12 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -27699,12 +27699,12 @@
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K447" t="inlineStr"/>
@@ -27714,13 +27714,13 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>6013.5</v>
+        <v>4086.85</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>2258-5910-CM26</t>
+          <t>2258-5950-CM26</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -27760,12 +27760,12 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K448" t="inlineStr"/>
@@ -27775,13 +27775,13 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>5162.29</v>
+        <v>9396.43</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>2258-5912-CM26</t>
+          <t>2258-5918-CM26</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -27821,12 +27821,12 @@
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>MEDIPLEX S A</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>86.383.300-0</t>
         </is>
       </c>
       <c r="K449" t="inlineStr"/>
@@ -27836,13 +27836,13 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>4246.51</v>
+        <v>31349.02</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>2258-5918-CM26</t>
+          <t>2258-5958-CM26</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -27882,12 +27882,12 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>MEDIPLEX S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>86.383.300-0</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K450" t="inlineStr"/>
@@ -27897,13 +27897,13 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>31131.15</v>
+        <v>5066.35</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>2258-5950-CM26</t>
+          <t>2258-5910-CM26</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -27943,12 +27943,12 @@
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K451" t="inlineStr"/>
@@ -27958,13 +27958,13 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>9331.129999999999</v>
+        <v>5198.41</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>2258-5958-CM26</t>
+          <t>2258-5912-CM26</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -28004,12 +28004,12 @@
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K452" t="inlineStr"/>
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>5031.14</v>
+        <v>4276.23</v>
       </c>
     </row>
     <row r="453">
@@ -28080,7 +28080,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>1062.98</v>
+        <v>1059.62</v>
       </c>
     </row>
     <row r="454">
@@ -28141,7 +28141,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>1174.03</v>
+        <v>1170.33</v>
       </c>
     </row>
     <row r="455">
@@ -28202,7 +28202,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>773.63</v>
+        <v>771.95</v>
       </c>
     </row>
     <row r="456">
@@ -28263,7 +28263,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>29676.51</v>
+        <v>29504.74</v>
       </c>
     </row>
     <row r="457">
@@ -28324,13 +28324,13 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>1945.73</v>
+        <v>1914.33</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>1261592-892-CM26</t>
+          <t>1261592-891-CM26</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -28385,13 +28385,13 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>1227.8</v>
+        <v>1914.33</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>1261592-891-CM26</t>
+          <t>2215-808-CM26</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -28411,17 +28411,17 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -28431,12 +28431,12 @@
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>Jocelyn</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>76.226.228-2</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K459" t="inlineStr"/>
@@ -28446,7 +28446,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>1945.73</v>
+        <v>30258.22</v>
       </c>
     </row>
     <row r="460">
@@ -28507,13 +28507,13 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>31547.9</v>
+        <v>31038.8</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>2215-808-CM26</t>
+          <t>1261592-892-CM26</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -28533,17 +28533,17 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
@@ -28553,12 +28553,12 @@
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>Jocelyn</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.226.228-2</t>
         </is>
       </c>
       <c r="K461" t="inlineStr"/>
@@ -28568,7 +28568,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>30754.53</v>
+        <v>1207.98</v>
       </c>
     </row>
     <row r="462">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>11737.6</v>
+        <v>11548.18</v>
       </c>
     </row>
     <row r="463">
@@ -28690,7 +28690,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>12695.32</v>
+        <v>12490.45</v>
       </c>
     </row>
     <row r="464">
@@ -28751,7 +28751,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>5146.56</v>
+        <v>5063.51</v>
       </c>
     </row>
     <row r="465">
@@ -28812,7 +28812,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>8971.299999999999</v>
+        <v>8826.530000000001</v>
       </c>
     </row>
     <row r="466">
@@ -28873,7 +28873,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>21032.76</v>
+        <v>20693.34</v>
       </c>
     </row>
     <row r="467">
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>5752.07</v>
+        <v>5659.84</v>
       </c>
     </row>
     <row r="468">
@@ -28995,7 +28995,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>5104.25</v>
+        <v>5022.42</v>
       </c>
     </row>
     <row r="469">
@@ -29056,13 +29056,13 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>1286.55</v>
+        <v>1265.92</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>2215-835-CM26</t>
+          <t>2215-832-CM26</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -29102,12 +29102,12 @@
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>FLEXING CHILE SPA</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.592.530-4</t>
         </is>
       </c>
       <c r="K470" t="inlineStr"/>
@@ -29117,13 +29117,13 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>781.14</v>
+        <v>3839.36</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>2215-832-CM26</t>
+          <t>2215-831-CM26</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -29163,12 +29163,12 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>FLEXING CHILE SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>76.592.530-4</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K471" t="inlineStr"/>
@@ -29178,13 +29178,13 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>3884.56</v>
+        <v>2773.59</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2215-831-CM26</t>
+          <t>2215-830-CM26</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -29224,12 +29224,12 @@
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K472" t="inlineStr"/>
@@ -29239,13 +29239,13 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>2806.24</v>
+        <v>7655.98</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2215-830-CM26</t>
+          <t>1261592-922-CM26</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -29265,17 +29265,17 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -29285,12 +29285,12 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K473" t="inlineStr"/>
@@ -29300,13 +29300,13 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>7746.11</v>
+        <v>10106.91</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>1261592-922-CM26</t>
+          <t>1261592-918-CM26</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -29346,12 +29346,12 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K474" t="inlineStr"/>
@@ -29361,13 +29361,13 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>10225.89</v>
+        <v>4611.28</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>1261592-918-CM26</t>
+          <t>1261592-920-CM26</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -29407,12 +29407,12 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K475" t="inlineStr"/>
@@ -29422,13 +29422,13 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>4665.56</v>
+        <v>940.25</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>1261592-920-CM26</t>
+          <t>1261592-919-CM26</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -29468,12 +29468,12 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K476" t="inlineStr"/>
@@ -29483,13 +29483,13 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>951.3099999999999</v>
+        <v>11223.72</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>1261592-919-CM26</t>
+          <t>4996-22-CM26</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -29514,12 +29514,12 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -29529,12 +29529,12 @@
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>IMPORTADORA PROMSA SPA</t>
         </is>
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>76.780.759-7</t>
         </is>
       </c>
       <c r="K477" t="inlineStr"/>
@@ -29544,13 +29544,13 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>11355.85</v>
+        <v>795.92</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>4996-22-CM26</t>
+          <t>2215-835-CM26</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -29570,17 +29570,17 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -29590,12 +29590,12 @@
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>IMPORTADORA PROMSA SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>76.780.759-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K478" t="inlineStr"/>
@@ -29605,7 +29605,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>805.29</v>
+        <v>772.05</v>
       </c>
     </row>
     <row r="479">
@@ -29666,7 +29666,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>5248.12</v>
+        <v>5187.05</v>
       </c>
     </row>
     <row r="480">
@@ -29727,7 +29727,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>4565.12</v>
+        <v>4542.68</v>
       </c>
     </row>
     <row r="481">
@@ -29788,7 +29788,190 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>13434.64</v>
+        <v>13524.56</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2258-5780-CM26</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>NEMO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr"/>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M482" s="2" t="n">
+        <v>4773.22</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>1057997-106-CM26</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>61.606.204-2</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>77.190.880-2</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr"/>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M483" s="2" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2258-6155-CM26</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr"/>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M484" s="2" t="n">
+        <v>1956.59</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/antofagasta.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/antofagasta.xlsx
@@ -623,7 +623,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +936,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1249,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1680,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1745,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1810,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +1997,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2062,11 @@
           <t>76.116.604-2</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2371,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2497,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2623,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2688,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2814,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3245,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3615,11 @@
           <t>76.116.604-2</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3802,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3867,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4298,11 @@
           <t>99.550.230-5</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4485,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4855,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5347,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5412,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5477,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5664,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6034,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6587,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6713,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6778,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7026,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7213,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7278,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7648,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +7957,11 @@
           <t>76.271.360-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8022,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8392,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8457,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8522,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8648,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +8835,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +8961,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9087,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9152,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9339,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9404,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +9957,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10022,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10087,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10213,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10339,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10404,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10591,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10656,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +10782,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +10847,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +10973,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11099,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11164,11 @@
           <t>77.430.568-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11229,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11294,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11420,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11485,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11672,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +11859,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12168,11 @@
           <t>76.116.604-2</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12294,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12359,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12668,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +12794,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +12981,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13107,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +13782,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14091,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14217,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14343,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14408,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +14717,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +14904,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +14969,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15217,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15526,11 @@
           <t>76.116.604-2</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +15652,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +15839,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +15965,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16030,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16095,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16221,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +16591,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +16656,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +16721,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +16786,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +16851,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +16977,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17347,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +17900,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +17965,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18030,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18095,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +18282,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +18591,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +18656,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +18782,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +18969,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19034,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19099,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19164,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +19534,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +19660,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +19725,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +19912,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +19977,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20042,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +20229,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +20538,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +20603,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +20668,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +20733,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +20920,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21107,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +21172,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +21237,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +21363,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +21672,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +21920,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +21985,11 @@
           <t>77.430.568-8</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22050,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22115,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +22302,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +22428,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +22554,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +22680,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +22745,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +22871,11 @@
           <t>76.780.759-7</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +23485,11 @@
           <t>77.883.662-9</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23010,7 +23550,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23193,7 +23737,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +23863,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23437,7 +23989,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +24115,11 @@
           <t>77.056.974-5</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +24180,11 @@
           <t>76.271.360-8</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +24245,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +24371,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +24619,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +24745,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +25115,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +25180,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +25245,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +25310,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +25497,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25389,7 +25989,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +26237,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25938,7 +26546,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +26916,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26426,7 +27042,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +27168,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +27233,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +27542,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +27607,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +27733,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +27798,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +28046,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27585,7 +28233,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27707,7 +28359,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27768,7 +28424,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +28489,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27890,7 +28554,11 @@
           <t>76.116.604-2</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +28619,11 @@
           <t>76.271.360-8</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28317,7 +28989,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +29054,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28439,7 +29119,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +29245,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +29737,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29537,7 +30229,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +30355,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30025,7 +30725,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30452,7 +31156,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30574,7 +31282,11 @@
           <t>77.305.553-K</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30635,7 +31347,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30757,7 +31473,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30879,7 +31599,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31123,7 +31847,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31245,7 +31973,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31306,7 +32038,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31733,7 +32469,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31916,7 +32656,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32038,7 +32782,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32099,7 +32847,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32160,7 +32912,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32465,7 +33221,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32526,7 +33286,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32831,7 +33595,11 @@
           <t>77.561.431-5</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32953,7 +33721,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33014,7 +33786,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33136,7 +33912,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33197,7 +33977,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33380,7 +34164,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33746,7 +34534,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33807,7 +34599,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33868,7 +34664,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34417,7 +35217,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34661,7 +35465,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34783,7 +35591,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34844,7 +35656,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34905,7 +35721,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35027,7 +35847,11 @@
           <t>77.056.974-5</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35210,7 +36034,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35271,7 +36099,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35454,7 +36286,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35576,7 +36412,11 @@
           <t>76.116.604-2</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35637,7 +36477,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35698,7 +36542,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35881,7 +36729,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35942,7 +36794,11 @@
           <t>99.569.670-3</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36003,7 +36859,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36247,7 +37107,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36369,7 +37233,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36430,7 +37298,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36491,7 +37363,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36674,7 +37550,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36735,7 +37615,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36796,7 +37680,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37101,7 +37989,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37345,7 +38237,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37528,7 +38424,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37894,7 +38794,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38077,7 +38981,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38138,7 +39046,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38382,7 +39294,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38443,7 +39359,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38687,7 +39607,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38931,7 +39855,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38992,7 +39920,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39358,7 +40290,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39724,7 +40660,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39846,7 +40786,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39907,7 +40851,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39968,7 +40916,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40090,7 +41042,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40151,7 +41107,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40212,7 +41172,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40334,7 +41298,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40456,7 +41424,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40700,7 +41672,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40944,7 +41920,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41005,7 +41985,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41127,7 +42111,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41249,7 +42237,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41310,7 +42302,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41554,7 +42550,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41676,7 +42676,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41798,7 +42802,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41859,7 +42867,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41920,7 +42932,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42042,7 +43058,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42469,7 +43489,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42530,7 +43554,11 @@
           <t>76.116.604-2</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42774,7 +43802,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42835,7 +43867,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42896,7 +43932,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43018,7 +44058,11 @@
           <t>77.430.568-8</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43140,7 +44184,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43201,7 +44249,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43262,7 +44314,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43506,7 +44562,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43567,7 +44627,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43994,7 +45058,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44177,7 +45245,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44421,7 +45493,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44543,7 +45619,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L723" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44604,7 +45684,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44787,7 +45871,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L727" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44848,7 +45936,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44970,7 +46062,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45031,7 +46127,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L731" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45153,7 +46253,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45275,7 +46379,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K735" t="inlineStr"/>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L735" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45458,7 +46566,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45702,7 +46814,11 @@
           <t>77.561.431-5</t>
         </is>
       </c>
-      <c r="K742" t="inlineStr"/>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L742" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45885,7 +47001,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L745" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45946,7 +47066,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K746" t="inlineStr"/>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L746" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46129,7 +47253,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46251,7 +47379,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K751" t="inlineStr"/>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L751" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46312,7 +47444,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K752" t="inlineStr"/>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L752" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46434,7 +47570,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46495,7 +47635,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K755" t="inlineStr"/>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L755" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46617,7 +47761,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K757" t="inlineStr"/>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L757" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46739,7 +47887,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K759" t="inlineStr"/>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L759" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46800,7 +47952,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K760" t="inlineStr"/>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L760" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46861,7 +48017,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K761" t="inlineStr"/>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L761" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46922,7 +48082,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K762" t="inlineStr"/>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L762" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46983,7 +48147,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K763" t="inlineStr"/>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L763" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47044,7 +48212,11 @@
           <t>77.568.114-4</t>
         </is>
       </c>
-      <c r="K764" t="inlineStr"/>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L764" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47166,7 +48338,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K766" t="inlineStr"/>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L766" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47227,7 +48403,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K767" t="inlineStr"/>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L767" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47288,7 +48468,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K768" t="inlineStr"/>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L768" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47349,7 +48533,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K769" t="inlineStr"/>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L769" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47410,7 +48598,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K770" t="inlineStr"/>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L770" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47471,7 +48663,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K771" t="inlineStr"/>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L771" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47654,7 +48850,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K774" t="inlineStr"/>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L774" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47715,7 +48915,11 @@
           <t>76.116.604-2</t>
         </is>
       </c>
-      <c r="K775" t="inlineStr"/>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L775" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47837,7 +49041,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K777" t="inlineStr"/>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L777" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47898,7 +49106,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K778" t="inlineStr"/>
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L778" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48020,7 +49232,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K780" t="inlineStr"/>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L780" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48691,7 +49907,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K791" t="inlineStr"/>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L791" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48874,7 +50094,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K794" t="inlineStr"/>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L794" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49240,7 +50464,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K800" t="inlineStr"/>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L800" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49301,7 +50529,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K801" t="inlineStr"/>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L801" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49484,7 +50716,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K804" t="inlineStr"/>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L804" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49606,7 +50842,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K806" t="inlineStr"/>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L806" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49667,7 +50907,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K807" t="inlineStr"/>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L807" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49728,7 +50972,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K808" t="inlineStr"/>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L808" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49789,7 +51037,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K809" t="inlineStr"/>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L809" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49850,7 +51102,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K810" t="inlineStr"/>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L810" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50094,7 +51350,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K814" t="inlineStr"/>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L814" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50216,7 +51476,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K816" t="inlineStr"/>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L816" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50277,7 +51541,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K817" t="inlineStr"/>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L817" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50521,7 +51789,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K821" t="inlineStr"/>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L821" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50582,7 +51854,11 @@
           <t>76.116.604-2</t>
         </is>
       </c>
-      <c r="K822" t="inlineStr"/>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L822" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50704,7 +51980,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K824" t="inlineStr"/>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L824" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50765,7 +52045,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K825" t="inlineStr"/>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L825" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50887,7 +52171,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K827" t="inlineStr"/>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L827" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50948,7 +52236,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K828" t="inlineStr"/>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L828" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51131,7 +52423,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K831" t="inlineStr"/>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L831" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51192,7 +52488,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K832" t="inlineStr"/>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L832" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51436,7 +52736,11 @@
           <t>77.430.568-8</t>
         </is>
       </c>
-      <c r="K836" t="inlineStr"/>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L836" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51558,7 +52862,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K838" t="inlineStr"/>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L838" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51680,7 +52988,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K840" t="inlineStr"/>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L840" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51802,7 +53114,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K842" t="inlineStr"/>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L842" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51924,7 +53240,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K844" t="inlineStr"/>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L844" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51985,7 +53305,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K845" t="inlineStr"/>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L845" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52473,7 +53797,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K853" t="inlineStr"/>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L853" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52717,7 +54045,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K857" t="inlineStr"/>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L857" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52778,7 +54110,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K858" t="inlineStr"/>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L858" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52839,7 +54175,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K859" t="inlineStr"/>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L859" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52961,7 +54301,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K861" t="inlineStr"/>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L861" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53022,7 +54366,11 @@
           <t>76.780.759-7</t>
         </is>
       </c>
-      <c r="K862" t="inlineStr"/>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L862" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53205,7 +54553,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K865" t="inlineStr"/>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L865" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53266,7 +54618,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K866" t="inlineStr"/>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L866" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53449,7 +54805,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K869" t="inlineStr"/>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L869" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53754,7 +55114,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K874" t="inlineStr"/>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L874" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53876,7 +55240,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K876" t="inlineStr"/>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L876" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54120,7 +55488,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K880" t="inlineStr"/>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L880" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54181,7 +55553,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K881" t="inlineStr"/>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L881" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54242,7 +55618,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K882" t="inlineStr"/>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L882" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54303,7 +55683,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K883" t="inlineStr"/>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L883" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54425,7 +55809,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K885" t="inlineStr"/>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L885" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54547,7 +55935,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K887" t="inlineStr"/>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L887" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54669,7 +56061,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K889" t="inlineStr"/>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L889" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54730,7 +56126,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K890" t="inlineStr"/>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L890" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54852,7 +56252,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K892" t="inlineStr"/>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L892" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54974,7 +56378,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K894" t="inlineStr"/>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L894" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55096,7 +56504,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K896" t="inlineStr"/>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L896" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55218,7 +56630,11 @@
           <t>77.561.431-5</t>
         </is>
       </c>
-      <c r="K898" t="inlineStr"/>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L898" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55279,7 +56695,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K899" t="inlineStr"/>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L899" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55340,7 +56760,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K900" t="inlineStr"/>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L900" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55645,7 +57069,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K905" t="inlineStr"/>
+      <c r="K905" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L905" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55767,7 +57195,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K907" t="inlineStr"/>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L907" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55889,7 +57321,11 @@
           <t>76.116.604-2</t>
         </is>
       </c>
-      <c r="K909" t="inlineStr"/>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L909" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55950,7 +57386,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K910" t="inlineStr"/>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L910" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56011,7 +57451,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K911" t="inlineStr"/>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L911" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56133,7 +57577,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K913" t="inlineStr"/>
+      <c r="K913" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L913" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56194,7 +57642,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K914" t="inlineStr"/>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L914" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56377,7 +57829,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K917" t="inlineStr"/>
+      <c r="K917" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L917" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56438,7 +57894,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K918" t="inlineStr"/>
+      <c r="K918" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L918" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56621,7 +58081,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K921" t="inlineStr"/>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L921" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56865,7 +58329,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K925" t="inlineStr"/>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L925" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56926,7 +58394,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K926" t="inlineStr"/>
+      <c r="K926" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L926" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57231,7 +58703,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K931" t="inlineStr"/>
+      <c r="K931" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L931" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57292,7 +58768,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K932" t="inlineStr"/>
+      <c r="K932" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L932" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57414,7 +58894,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K934" t="inlineStr"/>
+      <c r="K934" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L934" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57475,7 +58959,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K935" t="inlineStr"/>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L935" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57597,7 +59085,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K937" t="inlineStr"/>
+      <c r="K937" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L937" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57658,7 +59150,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K938" t="inlineStr"/>
+      <c r="K938" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L938" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57719,7 +59215,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K939" t="inlineStr"/>
+      <c r="K939" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L939" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57841,7 +59341,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K941" t="inlineStr"/>
+      <c r="K941" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L941" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57902,7 +59406,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K942" t="inlineStr"/>
+      <c r="K942" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L942" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57963,7 +59471,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K943" t="inlineStr"/>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L943" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58146,7 +59658,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K946" t="inlineStr"/>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L946" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58207,7 +59723,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K947" t="inlineStr"/>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L947" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58268,7 +59788,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K948" t="inlineStr"/>
+      <c r="K948" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L948" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58634,7 +60158,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K954" t="inlineStr"/>
+      <c r="K954" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L954" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59061,7 +60589,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K961" t="inlineStr"/>
+      <c r="K961" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L961" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59122,7 +60654,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K962" t="inlineStr"/>
+      <c r="K962" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L962" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59366,7 +60902,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K966" t="inlineStr"/>
+      <c r="K966" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L966" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59427,7 +60967,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K967" t="inlineStr"/>
+      <c r="K967" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L967" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59488,7 +61032,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K968" t="inlineStr"/>
+      <c r="K968" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L968" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59549,7 +61097,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K969" t="inlineStr"/>
+      <c r="K969" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L969" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59793,7 +61345,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K973" t="inlineStr"/>
+      <c r="K973" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L973" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59854,7 +61410,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K974" t="inlineStr"/>
+      <c r="K974" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L974" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59915,7 +61475,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K975" t="inlineStr"/>
+      <c r="K975" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L975" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59976,7 +61540,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K976" t="inlineStr"/>
+      <c r="K976" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L976" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60220,7 +61788,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K980" t="inlineStr"/>
+      <c r="K980" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L980" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60281,7 +61853,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K981" t="inlineStr"/>
+      <c r="K981" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L981" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/antofagasta.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/antofagasta.xlsx
@@ -62599,7 +62599,7 @@
       </c>
       <c r="E991" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F991" t="inlineStr">
@@ -63973,7 +63973,7 @@
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1013" t="inlineStr">
@@ -64095,7 +64095,7 @@
       </c>
       <c r="E1015" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1015" t="inlineStr">
